--- a/data/dividends_info_20260506.xlsx
+++ b/data/dividends_info_20260506.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>48.65999984741211</v>
+        <v>48.5</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1849568439831931</v>
+        <v>0.1855670103092784</v>
       </c>
       <c r="J2" t="n">
         <v>313</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>56.90000152587891</v>
+        <v>58</v>
       </c>
       <c r="I3" t="n">
-        <v>1.230228438010903</v>
+        <v>1.206896551724138</v>
       </c>
       <c r="J3" t="n">
         <v>292</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.699999809265137</v>
+        <v>9.800000190734863</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6185567131938485</v>
+        <v>0.6122448860432199</v>
       </c>
       <c r="J4" t="n">
         <v>222</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>48.65499877929688</v>
+        <v>48.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1849758550159409</v>
+        <v>0.1855670103092784</v>
       </c>
       <c r="J6" t="n">
         <v>222</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.069999933242798</v>
+        <v>2.075000047683716</v>
       </c>
       <c r="I7" t="n">
-        <v>3.719806883248261</v>
+        <v>3.710843288218411</v>
       </c>
       <c r="J7" t="n">
         <v>201</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5.900000095367432</v>
+        <v>5.920000076293945</v>
       </c>
       <c r="I8" t="n">
-        <v>3.389830453681454</v>
+        <v>3.378378334839559</v>
       </c>
       <c r="J8" t="n">
         <v>194</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5.179999828338623</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9652509972386709</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>152</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>48.65499877929688</v>
+        <v>48.5</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1849758550159409</v>
+        <v>0.1855670103092784</v>
       </c>
       <c r="J13" t="n">
         <v>138</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.929999828338623</v>
+        <v>6.039999961853027</v>
       </c>
       <c r="I16" t="n">
-        <v>4.215851724063898</v>
+        <v>4.139072873823361</v>
       </c>
       <c r="J16" t="n">
         <v>82</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>9.744999885559082</v>
+        <v>9.845999717712402</v>
       </c>
       <c r="I17" t="n">
-        <v>2.668034921019227</v>
+        <v>2.640666336118968</v>
       </c>
       <c r="J17" t="n">
         <v>75</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>15.84000015258789</v>
+        <v>15.72000026702881</v>
       </c>
       <c r="I18" t="n">
-        <v>3.787878751389872</v>
+        <v>3.816793828295553</v>
       </c>
       <c r="J18" t="n">
         <v>75</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3.779999971389771</v>
+        <v>3.726000070571899</v>
       </c>
       <c r="I19" t="n">
-        <v>5.820105864157292</v>
+        <v>5.904455067984807</v>
       </c>
       <c r="J19" t="n">
         <v>75</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6.09499979019165</v>
+        <v>6.170000076293945</v>
       </c>
       <c r="I21" t="n">
-        <v>3.937653950148101</v>
+        <v>3.889789254980977</v>
       </c>
       <c r="J21" t="n">
         <v>75</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>18.39999961853027</v>
+        <v>18.25</v>
       </c>
       <c r="I22" t="n">
-        <v>2.04347830323506</v>
+        <v>2.06027397260274</v>
       </c>
       <c r="J22" t="n">
         <v>75</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5.860000133514404</v>
+        <v>5.760000228881836</v>
       </c>
       <c r="I23" t="n">
-        <v>2.047781523309159</v>
+        <v>2.083333250549107</v>
       </c>
       <c r="J23" t="n">
         <v>68</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>9.350000381469727</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5347593364711767</v>
+        <v>0.5319149152031317</v>
       </c>
       <c r="J24" t="n">
         <v>68</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>4.130000114440918</v>
+        <v>4.03000020980835</v>
       </c>
       <c r="I26" t="n">
-        <v>1.694915207271755</v>
+        <v>1.736972614285023</v>
       </c>
       <c r="J26" t="n">
         <v>61</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>37</v>
+        <v>36.15000152587891</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4054054054054054</v>
+        <v>0.4149377418217221</v>
       </c>
       <c r="J27" t="n">
         <v>61</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5.900000095367432</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6779660907362907</v>
+        <v>0.6896551497342619</v>
       </c>
       <c r="J28" t="n">
         <v>54</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>23.21999931335449</v>
+        <v>23.55999946594238</v>
       </c>
       <c r="I29" t="n">
-        <v>4.091300723913577</v>
+        <v>4.032258155919278</v>
       </c>
       <c r="J29" t="n">
         <v>47</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>27.75</v>
+        <v>27.39999961853027</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7027027027027027</v>
+        <v>0.7116788420249611</v>
       </c>
       <c r="J30" t="n">
         <v>47</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.995000004768372</v>
+        <v>1.960000038146973</v>
       </c>
       <c r="I31" t="n">
-        <v>1.654135334392214</v>
+        <v>1.683673436618855</v>
       </c>
       <c r="J31" t="n">
         <v>47</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>5.090000152587891</v>
+        <v>5.125</v>
       </c>
       <c r="I32" t="n">
-        <v>5.697445801697203</v>
+        <v>5.658536585365853</v>
       </c>
       <c r="J32" t="n">
         <v>47</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>3.967999935150146</v>
+        <v>4.004000186920166</v>
       </c>
       <c r="I33" t="n">
-        <v>4.032258130416166</v>
+        <v>3.99600380945712</v>
       </c>
       <c r="J33" t="n">
         <v>47</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2.611999988555908</v>
+        <v>2.624000072479248</v>
       </c>
       <c r="I34" t="n">
-        <v>5.306278736878078</v>
+        <v>5.282012049223986</v>
       </c>
       <c r="J34" t="n">
         <v>47</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>54.33000183105469</v>
+        <v>55.95999908447266</v>
       </c>
       <c r="I35" t="n">
-        <v>1.159580303271582</v>
+        <v>1.125804164237035</v>
       </c>
       <c r="J35" t="n">
         <v>47</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>5.114999771118164</v>
+        <v>5.215000152587891</v>
       </c>
       <c r="I36" t="n">
-        <v>2.737048020813407</v>
+        <v>2.684563679840478</v>
       </c>
       <c r="J36" t="n">
         <v>47</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>19.54999923706055</v>
+        <v>19.79999923706055</v>
       </c>
       <c r="I37" t="n">
-        <v>3.989769976672784</v>
+        <v>3.939394091187837</v>
       </c>
       <c r="J37" t="n">
         <v>47</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>22.48999977111816</v>
+        <v>22.73999977111816</v>
       </c>
       <c r="I38" t="n">
-        <v>3.779457575146695</v>
+        <v>3.73790680983021</v>
       </c>
       <c r="J38" t="n">
         <v>47</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>48.65499877929688</v>
+        <v>48.5</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1849758550159409</v>
+        <v>0.1855670103092784</v>
       </c>
       <c r="J39" t="n">
         <v>47</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>6.553999900817871</v>
+        <v>6.60200023651123</v>
       </c>
       <c r="I40" t="n">
-        <v>2.766249660415399</v>
+        <v>2.746137435702462</v>
       </c>
       <c r="J40" t="n">
         <v>47</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>10.13000011444092</v>
+        <v>10.23999977111816</v>
       </c>
       <c r="I42" t="n">
-        <v>2.734452091516959</v>
+        <v>2.70507818546321</v>
       </c>
       <c r="J42" t="n">
         <v>47</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>3.766000032424927</v>
+        <v>3.677999973297119</v>
       </c>
       <c r="I44" t="n">
-        <v>2.920870925462288</v>
+        <v>2.99075586728162</v>
       </c>
       <c r="J44" t="n">
         <v>40</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>3.359999895095825</v>
+        <v>3.390000104904175</v>
       </c>
       <c r="I46" t="n">
-        <v>4.761904910578483</v>
+        <v>4.719763865745447</v>
       </c>
       <c r="J46" t="n">
         <v>33</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.9200000166893005</v>
+        <v>0.9150000214576721</v>
       </c>
       <c r="I47" t="n">
-        <v>2.71739125505287</v>
+        <v>2.73224037308468</v>
       </c>
       <c r="J47" t="n">
         <v>33</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>28.04999923706055</v>
+        <v>27.89999961853027</v>
       </c>
       <c r="I48" t="n">
-        <v>3.957219358970367</v>
+        <v>3.978494678052877</v>
       </c>
       <c r="J48" t="n">
         <v>29</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.5170000195503235</v>
+        <v>0.5139999985694885</v>
       </c>
       <c r="I50" t="n">
-        <v>4.448742578386158</v>
+        <v>4.47470818365977</v>
       </c>
       <c r="J50" t="n">
         <v>26</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>19.45000076293945</v>
+        <v>19.89999961853027</v>
       </c>
       <c r="I51" t="n">
-        <v>3.084832783879659</v>
+        <v>3.015075434681407</v>
       </c>
       <c r="J51" t="n">
         <v>26</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>2.559999942779541</v>
+        <v>2.565000057220459</v>
       </c>
       <c r="I53" t="n">
-        <v>7.031250157160687</v>
+        <v>7.017543703100556</v>
       </c>
       <c r="J53" t="n">
         <v>19</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>13.72000026702881</v>
+        <v>13.5600004196167</v>
       </c>
       <c r="I55" t="n">
-        <v>1.822157398938155</v>
+        <v>1.843657760056815</v>
       </c>
       <c r="J55" t="n">
         <v>19</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>3.410000085830688</v>
+        <v>3.420000076293945</v>
       </c>
       <c r="I56" t="n">
-        <v>0.8797653737504787</v>
+        <v>0.8771929628875695</v>
       </c>
       <c r="J56" t="n">
         <v>19</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>3.769999980926514</v>
+        <v>3.789999961853027</v>
       </c>
       <c r="I57" t="n">
-        <v>3.978779860978569</v>
+        <v>3.957783680996692</v>
       </c>
       <c r="J57" t="n">
         <v>19</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>13.64999961853027</v>
+        <v>14.35000038146973</v>
       </c>
       <c r="I58" t="n">
-        <v>4.249084367831286</v>
+        <v>4.041811739245378</v>
       </c>
       <c r="J58" t="n">
         <v>19</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.378999948501587</v>
+        <v>2.384000062942505</v>
       </c>
       <c r="I59" t="n">
-        <v>4.371584794085615</v>
+        <v>4.362415992205793</v>
       </c>
       <c r="J59" t="n">
         <v>12</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>11.47999954223633</v>
+        <v>11.21500015258789</v>
       </c>
       <c r="I60" t="n">
-        <v>2.526132504910426</v>
+        <v>2.585822523890753</v>
       </c>
       <c r="J60" t="n">
         <v>12</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>2.069999933242798</v>
+        <v>2.075000047683716</v>
       </c>
       <c r="I61" t="n">
-        <v>3.719806883248261</v>
+        <v>3.710843288218411</v>
       </c>
       <c r="J61" t="n">
         <v>12</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>38.90999984741211</v>
+        <v>39.09000015258789</v>
       </c>
       <c r="I62" t="n">
-        <v>4.214854809641115</v>
+        <v>4.195446389353433</v>
       </c>
       <c r="J62" t="n">
         <v>12</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>37.22999954223633</v>
+        <v>37.27000045776367</v>
       </c>
       <c r="I63" t="n">
-        <v>5.372011884477891</v>
+        <v>5.366246244795477</v>
       </c>
       <c r="J63" t="n">
         <v>12</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>4.00600004196167</v>
+        <v>3.818000078201294</v>
       </c>
       <c r="I64" t="n">
-        <v>2.496255590427595</v>
+        <v>2.619172287893488</v>
       </c>
       <c r="J64" t="n">
         <v>12</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>31.10000038146973</v>
+        <v>32.06999969482422</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4773633381961523</v>
+        <v>0.4629248562916575</v>
       </c>
       <c r="J65" t="n">
         <v>12</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>23.65999984741211</v>
+        <v>23.44000053405762</v>
       </c>
       <c r="I66" t="n">
-        <v>3.888419298111822</v>
+        <v>3.924914586342555</v>
       </c>
       <c r="J66" t="n">
         <v>12</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>8.819999694824219</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="I67" t="n">
-        <v>3.401360661906224</v>
+        <v>3.370786661331805</v>
       </c>
       <c r="J67" t="n">
         <v>12</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>85.26000213623047</v>
+        <v>84.72000122070312</v>
       </c>
       <c r="I68" t="n">
-        <v>1.219798233570606</v>
+        <v>1.227573164559698</v>
       </c>
       <c r="J68" t="n">
         <v>12</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>48.36000061035156</v>
+        <v>48.52999877929688</v>
       </c>
       <c r="I69" t="n">
-        <v>1.447477235660257</v>
+        <v>1.442406794987646</v>
       </c>
       <c r="J69" t="n">
         <v>12</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>56.90000152587891</v>
+        <v>58</v>
       </c>
       <c r="I70" t="n">
-        <v>3.866432233748553</v>
+        <v>3.793103448275863</v>
       </c>
       <c r="J70" t="n">
         <v>12</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>9.340000152587891</v>
+        <v>9.36299991607666</v>
       </c>
       <c r="I71" t="n">
-        <v>9.207708629016613</v>
+        <v>9.185090331180547</v>
       </c>
       <c r="J71" t="n">
         <v>12</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>13.14599990844727</v>
+        <v>13.13799953460693</v>
       </c>
       <c r="I72" t="n">
-        <v>4.259850934885213</v>
+        <v>4.262444967553078</v>
       </c>
       <c r="J72" t="n">
         <v>12</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>10.03999996185303</v>
+        <v>9.970000267028809</v>
       </c>
       <c r="I74" t="n">
-        <v>2.988047820118025</v>
+        <v>3.009027000652267</v>
       </c>
       <c r="J74" t="n">
         <v>12</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>2.200000047683716</v>
+        <v>2.210000038146973</v>
       </c>
       <c r="I75" t="n">
-        <v>4.909090802689231</v>
+        <v>4.886877743701542</v>
       </c>
       <c r="J75" t="n">
         <v>12</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>85.09999847412109</v>
+        <v>86.90000152587891</v>
       </c>
       <c r="I76" t="n">
-        <v>2.420681594520176</v>
+        <v>2.370540809929135</v>
       </c>
       <c r="J76" t="n">
         <v>12</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>15.77999973297119</v>
+        <v>15.69999980926514</v>
       </c>
       <c r="I77" t="n">
-        <v>4.752851791454268</v>
+        <v>4.777070121729542</v>
       </c>
       <c r="J77" t="n">
         <v>12</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>15.84000015258789</v>
+        <v>15.72000026702881</v>
       </c>
       <c r="I78" t="n">
-        <v>1.893939375694936</v>
+        <v>1.908396914147776</v>
       </c>
       <c r="J78" t="n">
         <v>12</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>45.79999923706055</v>
+        <v>48.90000152587891</v>
       </c>
       <c r="I79" t="n">
-        <v>1.855895227422177</v>
+        <v>1.738241254553258</v>
       </c>
       <c r="J79" t="n">
         <v>12</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>34.40000152587891</v>
+        <v>35.15999984741211</v>
       </c>
       <c r="I80" t="n">
-        <v>2.470930122955228</v>
+        <v>2.417519919479075</v>
       </c>
       <c r="J80" t="n">
         <v>12</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>62.56000137329102</v>
+        <v>62.86000061035156</v>
       </c>
       <c r="I81" t="n">
-        <v>2.078005069474014</v>
+        <v>2.068087794109758</v>
       </c>
       <c r="J81" t="n">
         <v>12</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>8.100000381469727</v>
+        <v>8.039999961853027</v>
       </c>
       <c r="I82" t="n">
-        <v>7.407407058555364</v>
+        <v>7.462686602572003</v>
       </c>
       <c r="J82" t="n">
         <v>12</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="I83" t="n">
-        <v>7.833333333333332</v>
+        <v>7.519999999999999</v>
       </c>
       <c r="J83" t="n">
         <v>12</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>5.900000095367432</v>
+        <v>5.920000076293945</v>
       </c>
       <c r="I84" t="n">
-        <v>3.389830453681454</v>
+        <v>3.378378334839559</v>
       </c>
       <c r="J84" t="n">
         <v>12</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>22.81999969482422</v>
+        <v>22.95999908447266</v>
       </c>
       <c r="I85" t="n">
-        <v>4.382121005140982</v>
+        <v>4.355400870535217</v>
       </c>
       <c r="J85" t="n">
         <v>12</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>4.730000019073486</v>
+        <v>4.75</v>
       </c>
       <c r="I86" t="n">
-        <v>4.545454527125229</v>
+        <v>4.526315789473684</v>
       </c>
       <c r="J86" t="n">
         <v>12</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>8.159999847412109</v>
+        <v>8.279999732971191</v>
       </c>
       <c r="I88" t="n">
-        <v>2.450980437988963</v>
+        <v>2.415459015096273</v>
       </c>
       <c r="J88" t="n">
         <v>12</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>9.454999923706055</v>
+        <v>9.470000267028809</v>
       </c>
       <c r="I89" t="n">
-        <v>2.538339523390792</v>
+        <v>2.534318830334093</v>
       </c>
       <c r="J89" t="n">
         <v>12</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>21.70999908447266</v>
+        <v>21.89999961853027</v>
       </c>
       <c r="I90" t="n">
-        <v>3.638876247420116</v>
+        <v>3.607305998907673</v>
       </c>
       <c r="J90" t="n">
         <v>12</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>5.179999828338623</v>
+        <v>5.199999809265137</v>
       </c>
       <c r="I91" t="n">
-        <v>1.795366854863928</v>
+        <v>1.788461604061919</v>
       </c>
       <c r="J91" t="n">
         <v>12</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>36.5</v>
+        <v>36.56000137329102</v>
       </c>
       <c r="I93" t="n">
-        <v>0.9589041095890409</v>
+        <v>0.9573303797950435</v>
       </c>
       <c r="J93" t="n">
         <v>12</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>7.235000133514404</v>
+        <v>7.335000038146973</v>
       </c>
       <c r="I94" t="n">
-        <v>7.661368206924256</v>
+        <v>7.556918842771156</v>
       </c>
       <c r="J94" t="n">
         <v>12</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>12.85000038146973</v>
+        <v>12.80000019073486</v>
       </c>
       <c r="I96" t="n">
-        <v>1.556420187258585</v>
+        <v>1.562499976716936</v>
       </c>
       <c r="J96" t="n">
         <v>12</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>6.59499979019165</v>
+        <v>7.320000171661377</v>
       </c>
       <c r="I97" t="n">
-        <v>1.56178928395397</v>
+        <v>1.40710379213861</v>
       </c>
       <c r="J97" t="n">
         <v>12</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>5.973999977111816</v>
+        <v>5.948999881744385</v>
       </c>
       <c r="I98" t="n">
-        <v>3.180448622831385</v>
+        <v>3.193814149888462</v>
       </c>
       <c r="J98" t="n">
         <v>12</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>10.32999992370605</v>
+        <v>10.46000003814697</v>
       </c>
       <c r="I99" t="n">
-        <v>4.181994222561553</v>
+        <v>4.130019105396967</v>
       </c>
       <c r="J99" t="n">
         <v>12</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>26.07999992370605</v>
+        <v>27.67000007629395</v>
       </c>
       <c r="I100" t="n">
-        <v>1.687116569352637</v>
+        <v>1.590169854668582</v>
       </c>
       <c r="J100" t="n">
         <v>12</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>8.539999961853027</v>
+        <v>8.579999923706055</v>
       </c>
       <c r="I102" t="n">
-        <v>5.503512905145475</v>
+        <v>5.477855526564943</v>
       </c>
       <c r="J102" t="n">
         <v>12</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>54.22000122070312</v>
+        <v>54.20000076293945</v>
       </c>
       <c r="I103" t="n">
-        <v>2.582072977647647</v>
+        <v>2.583025793898666</v>
       </c>
       <c r="J103" t="n">
         <v>12</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>4.136000156402588</v>
+        <v>4.13100004196167</v>
       </c>
       <c r="I104" t="n">
-        <v>7.253384638673083</v>
+        <v>7.262164051141967</v>
       </c>
       <c r="J104" t="n">
         <v>12</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>12.75</v>
+        <v>12.80000019073486</v>
       </c>
       <c r="I105" t="n">
-        <v>0.9411764705882352</v>
+        <v>0.9374999860301615</v>
       </c>
       <c r="J105" t="n">
         <v>12</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>3.480000019073486</v>
+        <v>3.420000076293945</v>
       </c>
       <c r="I106" t="n">
-        <v>4.885057444489921</v>
+        <v>4.970760123029561</v>
       </c>
       <c r="J106" t="n">
         <v>12</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>21.85000038146973</v>
+        <v>21.04999923706055</v>
       </c>
       <c r="I107" t="n">
-        <v>3.203661271299781</v>
+        <v>3.325415797486504</v>
       </c>
       <c r="J107" t="n">
         <v>12</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>2.5</v>
+        <v>2.440000057220459</v>
       </c>
       <c r="I108" t="n">
-        <v>1.4</v>
+        <v>1.434426195869457</v>
       </c>
       <c r="J108" t="n">
         <v>12</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>6.099999904632568</v>
+        <v>6.119999885559082</v>
       </c>
       <c r="I109" t="n">
-        <v>5.409836150151177</v>
+        <v>5.392156963575718</v>
       </c>
       <c r="J109" t="n">
         <v>12</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>0.9760000109672546</v>
+        <v>0.9779999852180481</v>
       </c>
       <c r="I110" t="n">
-        <v>7.172131066948169</v>
+        <v>7.157464320860218</v>
       </c>
       <c r="J110" t="n">
         <v>12</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>49.84000015258789</v>
+        <v>49.90000152587891</v>
       </c>
       <c r="I111" t="n">
-        <v>1.424558583118572</v>
+        <v>1.422845647873945</v>
       </c>
       <c r="J111" t="n">
         <v>12</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>99.34999847412109</v>
+        <v>99.65000152587891</v>
       </c>
       <c r="I112" t="n">
-        <v>1.358832431539142</v>
+        <v>1.354741574840225</v>
       </c>
       <c r="J112" t="n">
         <v>12</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>7.179999828338623</v>
+        <v>7.139999866485596</v>
       </c>
       <c r="I113" t="n">
-        <v>1.114206154772446</v>
+        <v>1.120448200223526</v>
       </c>
       <c r="J113" t="n">
         <v>12</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="I114" t="n">
-        <v>1.171875</v>
+        <v>1.2</v>
       </c>
       <c r="J114" t="n">
         <v>12</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>4.589000225067139</v>
+        <v>4.592000007629395</v>
       </c>
       <c r="I115" t="n">
-        <v>3.704510604976335</v>
+        <v>3.702090586183644</v>
       </c>
       <c r="J115" t="n">
         <v>12</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>57.79999923706055</v>
+        <v>57</v>
       </c>
       <c r="I117" t="n">
-        <v>0.7785467230793082</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="J117" t="n">
         <v>12</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>5.199999809265137</v>
+        <v>5.139999866485596</v>
       </c>
       <c r="I118" t="n">
-        <v>0.7692307974459868</v>
+        <v>0.7782101369459655</v>
       </c>
       <c r="J118" t="n">
         <v>12</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>33.65999984741211</v>
+        <v>33.77999877929688</v>
       </c>
       <c r="I119" t="n">
-        <v>3.119429604158859</v>
+        <v>3.108348247317064</v>
       </c>
       <c r="J119" t="n">
         <v>12</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>19.82999992370605</v>
+        <v>21.31999969482422</v>
       </c>
       <c r="I121" t="n">
-        <v>1.916288459213374</v>
+        <v>1.782364002998796</v>
       </c>
       <c r="J121" t="n">
         <v>12</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>26.57999992370605</v>
+        <v>26.54000091552734</v>
       </c>
       <c r="I122" t="n">
-        <v>2.257336349594473</v>
+        <v>2.260738429925853</v>
       </c>
       <c r="J122" t="n">
         <v>12</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>34.59999847412109</v>
+        <v>33.79999923706055</v>
       </c>
       <c r="I123" t="n">
-        <v>1.011560738252</v>
+        <v>1.035502981953434</v>
       </c>
       <c r="J123" t="n">
         <v>12</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>3.559999942779541</v>
+        <v>3.599999904632568</v>
       </c>
       <c r="I124" t="n">
-        <v>0.4775280975630273</v>
+        <v>0.4722222347318393</v>
       </c>
       <c r="J124" t="n">
         <v>12</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>2.890000104904175</v>
+        <v>2.900000095367432</v>
       </c>
       <c r="I125" t="n">
-        <v>0.3460207486854598</v>
+        <v>0.3448275748671309</v>
       </c>
       <c r="J125" t="n">
         <v>12</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>22.48999977111816</v>
+        <v>22.30999946594238</v>
       </c>
       <c r="I126" t="n">
-        <v>4.979991157840353</v>
+        <v>5.02017044738056</v>
       </c>
       <c r="J126" t="n">
         <v>12</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>1.570000052452087</v>
+        <v>1.600000023841858</v>
       </c>
       <c r="I127" t="n">
-        <v>6.369426538796359</v>
+        <v>6.249999906867744</v>
       </c>
       <c r="J127" t="n">
         <v>12</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>8.760000228881836</v>
+        <v>8.680000305175781</v>
       </c>
       <c r="I128" t="n">
-        <v>2.968036452131321</v>
+        <v>2.995391599755649</v>
       </c>
       <c r="J128" t="n">
         <v>12</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>2.220000028610229</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I129" t="n">
-        <v>4.157657604075883</v>
+        <v>4.395238294839327</v>
       </c>
       <c r="J129" t="n">
         <v>12</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>9.439999580383301</v>
+        <v>9.420000076293945</v>
       </c>
       <c r="I130" t="n">
-        <v>3.707627283451517</v>
+        <v>3.715498908336511</v>
       </c>
       <c r="J130" t="n">
         <v>5</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>5.150000095367432</v>
+        <v>5.050000190734863</v>
       </c>
       <c r="I131" t="n">
-        <v>1.86407763538402</v>
+        <v>1.900990027210877</v>
       </c>
       <c r="J131" t="n">
         <v>5</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>9.699999809265137</v>
+        <v>9.800000190734863</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6185567131938485</v>
+        <v>0.6122448860432199</v>
       </c>
       <c r="J134" t="n">
         <v>5</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>19.89999961853027</v>
+        <v>19.60000038146973</v>
       </c>
       <c r="I135" t="n">
-        <v>2.512562862234506</v>
+        <v>2.551020358513417</v>
       </c>
       <c r="J135" t="n">
         <v>5</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>16.71999931335449</v>
+        <v>16.78000068664551</v>
       </c>
       <c r="I137" t="n">
-        <v>2.990430744818531</v>
+        <v>2.97973766114282</v>
       </c>
       <c r="J137" t="n">
         <v>5</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>3.980000019073486</v>
+        <v>4.059999942779541</v>
       </c>
       <c r="I138" t="n">
-        <v>2.512562802029314</v>
+        <v>2.463054221905688</v>
       </c>
       <c r="J138" t="n">
         <v>5</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>9.050000190734863</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="I140" t="n">
-        <v>0.9392264995421837</v>
+        <v>0.923913062632873</v>
       </c>
       <c r="J140" t="n">
         <v>5</v>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>1.269999980926514</v>
+        <v>1.240000009536743</v>
       </c>
       <c r="I142" t="n">
-        <v>2.362204759886205</v>
+        <v>2.419354820102608</v>
       </c>
       <c r="J142" t="n">
         <v>5</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>7.449999809265137</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="I143" t="n">
-        <v>1.208053722203753</v>
+        <v>1.184210541175673</v>
       </c>
       <c r="J143" t="n">
         <v>5</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>7.039999961853027</v>
+        <v>7.210000038146973</v>
       </c>
       <c r="I145" t="n">
-        <v>3.125000016933138</v>
+        <v>3.05131759828037</v>
       </c>
       <c r="J145" t="n">
         <v>5</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>26.35000038146973</v>
+        <v>26.29999923706055</v>
       </c>
       <c r="I146" t="n">
-        <v>2.314990478819781</v>
+        <v>2.319391702264465</v>
       </c>
       <c r="J146" t="n">
         <v>-2</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>3.039999961853027</v>
+        <v>3.019999980926514</v>
       </c>
       <c r="I147" t="n">
-        <v>4.934210588231972</v>
+        <v>4.966887448588033</v>
       </c>
       <c r="J147" t="n">
         <v>-2</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>11.94999980926514</v>
+        <v>11.69999980926514</v>
       </c>
       <c r="I148" t="n">
-        <v>5.857740679269905</v>
+        <v>5.982906080440066</v>
       </c>
       <c r="J148" t="n">
         <v>-2</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>8.819999694824219</v>
+        <v>8.710000038146973</v>
       </c>
       <c r="I149" t="n">
-        <v>5.787982059677091</v>
+        <v>5.86107919361855</v>
       </c>
       <c r="J149" t="n">
         <v>-2</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>8.260000228881836</v>
+        <v>8.029999732971191</v>
       </c>
       <c r="I150" t="n">
-        <v>3.268765042595528</v>
+        <v>3.362391145436526</v>
       </c>
       <c r="J150" t="n">
         <v>-2</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>5.914999961853027</v>
+        <v>5.775000095367432</v>
       </c>
       <c r="I151" t="n">
-        <v>5.917159801474511</v>
+        <v>6.060605960522177</v>
       </c>
       <c r="J151" t="n">
         <v>-2</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>17.70000076293945</v>
+        <v>17.85000038146973</v>
       </c>
       <c r="I153" t="n">
-        <v>4.237287952949482</v>
+        <v>4.20168058247541</v>
       </c>
       <c r="J153" t="n">
         <v>-2</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>11.55000019073486</v>
+        <v>11.69999980926514</v>
       </c>
       <c r="I154" t="n">
-        <v>3.722943661463623</v>
+        <v>3.675213735127469</v>
       </c>
       <c r="J154" t="n">
         <v>-2</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>4.204999923706055</v>
+        <v>4.210000038146973</v>
       </c>
       <c r="I155" t="n">
-        <v>3.567181990999854</v>
+        <v>3.562945335887036</v>
       </c>
       <c r="J155" t="n">
         <v>-2</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>12.15999984741211</v>
+        <v>12.22000026702881</v>
       </c>
       <c r="I156" t="n">
-        <v>1.62145561245185</v>
+        <v>1.613494236428032</v>
       </c>
       <c r="J156" t="n">
         <v>-2</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>28.54999923706055</v>
+        <v>28.60000038146973</v>
       </c>
       <c r="I157" t="n">
-        <v>3.852889770210915</v>
+        <v>3.846153794853453</v>
       </c>
       <c r="J157" t="n">
         <v>-2</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>57.09999847412109</v>
+        <v>57.79999923706055</v>
       </c>
       <c r="I158" t="n">
-        <v>0.8231173599996043</v>
+        <v>0.8131487996606106</v>
       </c>
       <c r="J158" t="n">
         <v>-2</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>78.09999847412109</v>
+        <v>77.19999694824219</v>
       </c>
       <c r="I159" t="n">
-        <v>1.536491707355958</v>
+        <v>1.55440420652416</v>
       </c>
       <c r="J159" t="n">
         <v>-2</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>25.85000038146973</v>
+        <v>26.45000076293945</v>
       </c>
       <c r="I160" t="n">
-        <v>1.044487412052599</v>
+        <v>1.020793921406278</v>
       </c>
       <c r="J160" t="n">
         <v>-2</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>10.30000019073486</v>
+        <v>10.44999980926514</v>
       </c>
       <c r="I161" t="n">
-        <v>3.689320320030873</v>
+        <v>3.636363702735056</v>
       </c>
       <c r="J161" t="n">
         <v>-2</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>30.10000038146973</v>
+        <v>28.89999961853027</v>
       </c>
       <c r="I162" t="n">
-        <v>0.996677728232479</v>
+        <v>1.038062297439078</v>
       </c>
       <c r="J162" t="n">
         <v>-2</v>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>0.1861999928951263</v>
+        <v>0.1858000010251999</v>
       </c>
       <c r="I163" t="n">
-        <v>3.759398639688788</v>
+        <v>3.767491906014896</v>
       </c>
       <c r="J163" t="n">
         <v>-9</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>7.179999828338623</v>
+        <v>6.889999866485596</v>
       </c>
       <c r="I164" t="n">
-        <v>2.228412309544892</v>
+        <v>2.322206140790707</v>
       </c>
       <c r="J164" t="n">
         <v>-9</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>2.194999933242798</v>
+        <v>2.174999952316284</v>
       </c>
       <c r="I165" t="n">
-        <v>2.961275716485869</v>
+        <v>2.988505812645086</v>
       </c>
       <c r="J165" t="n">
         <v>-9</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>6.960000038146973</v>
+        <v>7.239999771118164</v>
       </c>
       <c r="I168" t="n">
-        <v>7.183908006602824</v>
+        <v>6.906077566391673</v>
       </c>
       <c r="J168" t="n">
         <v>-16</v>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>19.13999938964844</v>
+        <v>19.15999984741211</v>
       </c>
       <c r="I169" t="n">
-        <v>3.396029366393512</v>
+        <v>3.392484369397288</v>
       </c>
       <c r="J169" t="n">
         <v>-16</v>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>12.75500011444092</v>
+        <v>12.77999973297119</v>
       </c>
       <c r="I170" t="n">
-        <v>4.233633831085775</v>
+        <v>4.225352200961719</v>
       </c>
       <c r="J170" t="n">
         <v>-16</v>
@@ -8466,10 +8466,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>6.407999992370605</v>
+        <v>6.546000003814697</v>
       </c>
       <c r="I171" t="n">
-        <v>1.560549315216299</v>
+        <v>1.527650472681405</v>
       </c>
       <c r="J171" t="n">
         <v>-16</v>
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>9.319999694824219</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="I172" t="n">
-        <v>1.716738253638083</v>
+        <v>1.702127728650021</v>
       </c>
       <c r="J172" t="n">
         <v>-16</v>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>287.2000122070312</v>
+        <v>286.1000061035156</v>
       </c>
       <c r="I173" t="n">
-        <v>1.258704681876576</v>
+        <v>1.263544188353507</v>
       </c>
       <c r="J173" t="n">
         <v>-16</v>
@@ -8607,10 +8607,10 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>31.79999923706055</v>
+        <v>30.70000076293945</v>
       </c>
       <c r="I174" t="n">
-        <v>4.276729662354899</v>
+        <v>4.429967316618995</v>
       </c>
       <c r="J174" t="n">
         <v>-16</v>
@@ -8654,10 +8654,10 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>13.98499965667725</v>
+        <v>13.97000026702881</v>
       </c>
       <c r="I175" t="n">
-        <v>41.62745901263167</v>
+        <v>41.67215382049638</v>
       </c>
       <c r="J175" t="n">
         <v>-16</v>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>16.6200008392334</v>
+        <v>16.21999931335449</v>
       </c>
       <c r="I176" t="n">
-        <v>3.519855417931395</v>
+        <v>3.606658599044138</v>
       </c>
       <c r="J176" t="n">
         <v>-16</v>
@@ -8748,10 +8748,10 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>20.42000007629395</v>
+        <v>20.52000045776367</v>
       </c>
       <c r="I177" t="n">
-        <v>3.085210566337763</v>
+        <v>3.070175370106494</v>
       </c>
       <c r="J177" t="n">
         <v>-16</v>
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>138.5</v>
+        <v>143.8000030517578</v>
       </c>
       <c r="I178" t="n">
-        <v>0.6498194945848376</v>
+        <v>0.6258692495827443</v>
       </c>
       <c r="J178" t="n">
         <v>-16</v>
@@ -8842,10 +8842,10 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>71.23000335693359</v>
+        <v>70.94000244140625</v>
       </c>
       <c r="I179" t="n">
-        <v>2.415835910293406</v>
+        <v>2.425711785704145</v>
       </c>
       <c r="J179" t="n">
         <v>-16</v>
@@ -8889,10 +8889,10 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>26.5</v>
+        <v>27</v>
       </c>
       <c r="I180" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5185185185185186</v>
       </c>
       <c r="J180" t="n">
         <v>-23</v>
@@ -8936,10 +8936,10 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>1.5</v>
+        <v>1.519999980926514</v>
       </c>
       <c r="I181" t="n">
-        <v>4</v>
+        <v>3.947368470585578</v>
       </c>
       <c r="J181" t="n">
         <v>-23</v>
@@ -9468,14 +9468,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -9485,14 +9485,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -9502,14 +9502,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -9519,14 +9519,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -9536,14 +9536,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9553,14 +9553,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9570,14 +9570,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -9587,14 +9587,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9611,7 +9611,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -9628,7 +9628,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -9655,14 +9655,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -9672,14 +9672,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -9696,7 +9696,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -9706,14 +9706,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9730,7 +9730,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9740,14 +9740,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9883,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -9900,7 +9900,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -9917,7 +9917,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10104,7 +10104,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -10114,14 +10114,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10155,7 +10155,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -10223,7 +10223,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10233,14 +10233,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -10342,7 +10342,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10471,14 +10471,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10488,14 +10488,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10512,7 +10512,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10522,7 +10522,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10556,14 +10556,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10573,14 +10573,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10590,14 +10590,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10607,14 +10607,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10631,7 +10631,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10641,14 +10641,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10658,14 +10658,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10675,14 +10675,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10699,7 +10699,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10716,7 +10716,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10726,14 +10726,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10743,14 +10743,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10767,7 +10767,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10777,14 +10777,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10794,14 +10794,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10811,14 +10811,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10828,14 +10828,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -10869,7 +10869,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10879,14 +10879,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10903,7 +10903,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10913,14 +10913,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10930,14 +10930,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10947,14 +10947,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10971,7 +10971,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10988,7 +10988,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10998,14 +10998,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11015,14 +11015,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11032,14 +11032,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11056,7 +11056,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11066,14 +11066,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11090,7 +11090,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11100,14 +11100,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11124,7 +11124,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11134,14 +11134,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11151,14 +11151,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11175,7 +11175,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11185,14 +11185,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11209,7 +11209,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11219,14 +11219,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -11253,14 +11253,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11277,7 +11277,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11287,14 +11287,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11304,14 +11304,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11328,7 +11328,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11345,7 +11345,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11355,14 +11355,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11372,14 +11372,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11389,14 +11389,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11406,14 +11406,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11423,14 +11423,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11447,7 +11447,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11464,7 +11464,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11481,7 +11481,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11491,14 +11491,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11508,14 +11508,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11532,7 +11532,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11542,14 +11542,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11566,7 +11566,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11583,7 +11583,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11593,14 +11593,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11719,7 +11719,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11729,14 +11729,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11746,14 +11746,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11770,7 +11770,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11787,7 +11787,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11804,7 +11804,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11814,14 +11814,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11831,14 +11831,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11855,7 +11855,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11872,7 +11872,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11889,7 +11889,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11899,14 +11899,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11923,7 +11923,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11940,7 +11940,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11957,7 +11957,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11974,7 +11974,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11984,14 +11984,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -12008,7 +12008,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12025,7 +12025,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12035,7 +12035,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -12059,7 +12059,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12069,14 +12069,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12093,7 +12093,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12110,7 +12110,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12120,14 +12120,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12144,7 +12144,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12161,7 +12161,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12178,7 +12178,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12195,7 +12195,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12205,14 +12205,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12222,14 +12222,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12246,7 +12246,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12256,14 +12256,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12273,14 +12273,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12290,14 +12290,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12314,7 +12314,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12324,14 +12324,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12341,14 +12341,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12358,14 +12358,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12375,14 +12375,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12399,7 +12399,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12416,7 +12416,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12426,14 +12426,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12443,14 +12443,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12460,14 +12460,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12477,14 +12477,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12494,14 +12494,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12518,7 +12518,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12528,14 +12528,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12545,14 +12545,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12562,14 +12562,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12579,14 +12579,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12596,14 +12596,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12613,14 +12613,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12630,14 +12630,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12654,7 +12654,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12664,14 +12664,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12688,7 +12688,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12705,7 +12705,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12715,14 +12715,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12732,14 +12732,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12749,14 +12749,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12773,7 +12773,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12790,7 +12790,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12800,14 +12800,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12824,7 +12824,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12834,14 +12834,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12875,7 +12875,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12892,7 +12892,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12902,7 +12902,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -12943,7 +12943,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>DIADEMA CAPITAL</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12953,14 +12953,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12977,7 +12977,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>DIADEMA CAPITAL</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -13028,7 +13028,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -13038,14 +13038,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -13055,14 +13055,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -13079,7 +13079,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -13096,7 +13096,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -13106,14 +13106,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -13123,14 +13123,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -13140,14 +13140,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -13157,7 +13157,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -13242,14 +13242,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -13259,14 +13259,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -13276,14 +13276,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -13293,14 +13293,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -13310,14 +13310,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -13351,7 +13351,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -13361,14 +13361,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -13385,7 +13385,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -13402,7 +13402,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -13419,7 +13419,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -13538,7 +13538,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -13555,7 +13555,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -13623,7 +13623,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -13633,14 +13633,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -13657,7 +13657,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -13667,14 +13667,14 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -13708,7 +13708,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -13725,7 +13725,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -13742,7 +13742,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -13752,14 +13752,14 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -13776,7 +13776,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -13786,14 +13786,14 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -13810,7 +13810,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13820,14 +13820,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -13837,14 +13837,14 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -13861,7 +13861,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -13878,7 +13878,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -13888,14 +13888,14 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13905,14 +13905,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13929,7 +13929,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13939,14 +13939,14 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13963,7 +13963,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13980,7 +13980,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13997,7 +13997,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -14007,14 +14007,14 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -14024,14 +14024,14 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -14041,14 +14041,14 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -14065,7 +14065,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -14075,14 +14075,14 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -14092,14 +14092,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -14109,14 +14109,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -14133,7 +14133,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -14150,7 +14150,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -14160,14 +14160,14 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -14177,14 +14177,14 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -14201,7 +14201,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -14211,14 +14211,14 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -14252,7 +14252,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -14269,7 +14269,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -14286,7 +14286,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -14303,7 +14303,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -14375,163 +14375,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>B.F. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Esprinet S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>OLIDATA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Piu' Medical S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>RAI WAY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Svas Biosana S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>